--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -54,148 +54,10 @@
     <x:t>TestCase_Name</x:t>
   </x:si>
   <x:si>
-    <x:t>Tests\Desktop Application\OrderFromApplication_TestCase.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Desktop Scenario</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\EriBank Mobile Application\EriBank Android Application\Android_MultipleScreen_TC.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Android Multiple Scenario</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\EriBank Mobile Application\EriBank Android Application\Android_LoginLogout_TC.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Android Login_Logout Scenario</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\EriBank Mobile Application\EriBank IOS Application\IOS_MultipleScreen Test Case.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IOS Multiple Scenario</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\EriBank Mobile Application\EriBank IOS Application\IOS_LoginLogout Test Case.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IOS Login_Logout Scenario</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\JsonPlaceholder API Tests\ApiFail_TestCase.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ApiTest Fail Scenario</x:t>
-  </x:si>
-  <x:si>
     <x:t>Tests\JsonPlaceholder API Tests\ApiPass_TestCase.xaml</x:t>
   </x:si>
   <x:si>
     <x:t>ApiTest  Pass Scenario</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\SAP Shopping Cart Application\SAP_AddtoCart Test Case.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAP Add to cart Scenario</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\SalesForce\SalesForce Application.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SalesForce Application Scenario</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_CartTC_90.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_CartTC_90</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_CartTC_95.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_CartTC_95</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_CheckoutTC_160.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_CheckoutTC_160</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_HomePageTC_506.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_HomePageTC_506</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_ReviewTC_174.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_ReviewTC_174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_ReviewTC_175.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_ReviewTC_175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_LoginTC_207.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_LoginTC_207</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_LoginTC_211.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_LoginTC_211</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_LoginTC_231.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_LoginTC_231</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_LoginTC_239.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_LoginTC_239</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_OrderTC_159.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_OrderTC_159</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_RegistrationTC_277.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_RegistrationTC_277</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_ShippingTC_502.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_ShippingTC_502</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_WishlistTC_183.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_WishlistTC_183</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tests\Web Application\Ecommerce Application\ECOM_WishlistTC_186.xaml</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOM_WishlistTC_186</x:t>
   </x:si>
   <x:si>
     <x:t>FLAG</x:t>
@@ -734,13 +596,151 @@
     <x:t>Column2</x:t>
   </x:si>
   <x:si>
+    <x:t>Test execution for ApiTest  Pass Scenario started 09/06/2024 16:15:05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test execution for ApiTest  Pass Scenario ended 09/06/2024 16:15:08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\EriBank Mobile Application\EriBank Android Application\Android_MultipleScreen_TC.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Android Multiple Scenario</x:t>
+  </x:si>
+  <x:si>
     <x:t>Flag status - disabled</x:t>
   </x:si>
   <x:si>
-    <x:t>Test execution for ApiTest  Pass Scenario started 09/05/2024 15:29:51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Test execution for ApiTest  Pass Scenario ended 09/05/2024 15:29:54</x:t>
+    <x:t>Tests\EriBank Mobile Application\EriBank Android Application\Android_LoginLogout_TC.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Android Login_Logout Scenario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\EriBank Mobile Application\EriBank IOS Application\IOS_MultipleScreen Test Case.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IOS Multiple Scenario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\EriBank Mobile Application\EriBank IOS Application\IOS_LoginLogout Test Case.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IOS Login_Logout Scenario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\JsonPlaceholder API Tests\ApiFail_TestCase.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ApiTest Fail Scenario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test execution for ApiTest  Pass Scenario started 09/06/2024 14:35:16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test execution for ApiTest  Pass Scenario ended 09/06/2024 14:35:19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\SAP Shopping Cart Application\SAP_AddtoCart Test Case.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAP Add to cart Scenario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\SalesForce\SalesForce Application.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SalesForce Application Scenario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_CartTC_90.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_CartTC_90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_CartTC_95.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_CartTC_95</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_CheckoutTC_160.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_CheckoutTC_160</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_HomePageTC_506.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_HomePageTC_506</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_ReviewTC_174.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_ReviewTC_174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_ReviewTC_175.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_ReviewTC_175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_LoginTC_207.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_LoginTC_207</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_LoginTC_211.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_LoginTC_211</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_LoginTC_231.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_LoginTC_231</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_LoginTC_239.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_LoginTC_239</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_OrderTC_159.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_OrderTC_159</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_RegistrationTC_277.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_RegistrationTC_277</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_ShippingTC_502.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_ShippingTC_502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_WishlistTC_183.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_WishlistTC_183</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tests\Web Application\Ecommerce Application\ECOM_WishlistTC_186.xaml</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOM_WishlistTC_186</x:t>
   </x:si>
   <x:si>
     <x:t>TestCaseID</x:t>
@@ -2067,7 +2067,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C25"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultColWidth="255" defaultRowHeight="14.5"/>
   <x:cols>
     <x:col min="1" max="1" width="14.909091" style="0" customWidth="1"/>
@@ -2076,7 +2076,7 @@
     <x:col min="4" max="4" width="8.909091" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:4">
+    <x:row r="1" spans="1:4" customFormat="1" ht="15" customHeight="1">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -2089,266 +2089,13 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:4">
-      <x:c r="A3" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:4">
-      <x:c r="A4" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:4">
-      <x:c r="A5" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:4">
-      <x:c r="A6" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:4">
-      <x:c r="A7" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:4">
-      <x:c r="A8" s="0" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:4">
-      <x:c r="A9" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:4">
-      <x:c r="A10" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:4" customFormat="1" ht="14" customHeight="1">
-      <x:c r="A11" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:4">
-      <x:c r="A12" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:4">
-      <x:c r="A13" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:4">
-      <x:c r="A14" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:4">
-      <x:c r="A15" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:4">
-      <x:c r="A16" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:4">
-      <x:c r="A17" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:4">
-      <x:c r="A18" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:4">
-      <x:c r="A19" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:4">
-      <x:c r="A20" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:4">
-      <x:c r="A21" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:4">
-      <x:c r="A22" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:4">
-      <x:c r="A23" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:4">
-      <x:c r="A24" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:4">
-      <x:c r="A25" s="0" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2383,77 +2130,77 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="13" t="s">
-        <x:v>190</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B1" s="13" t="s">
-        <x:v>191</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C1" s="13" t="s">
-        <x:v>130</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D1" s="13" t="s">
-        <x:v>192</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E1" s="13" t="s">
-        <x:v>193</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="F1" s="13" t="s">
-        <x:v>194</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G1" s="13" t="s">
-        <x:v>195</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H1" s="13" t="s">
-        <x:v>196</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="I1" s="13" t="s">
-        <x:v>71</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J1" s="13" t="s">
-        <x:v>72</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K1" s="13" t="s">
-        <x:v>197</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11" customFormat="1" ht="58" customHeight="1">
       <x:c r="A2" s="14" t="s">
-        <x:v>198</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B2" s="15" t="s">
-        <x:v>199</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C2" s="16" t="s">
-        <x:v>200</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D2" s="17" t="s">
-        <x:v>201</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E2" s="17" t="s">
-        <x:v>202</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="F2" s="13" t="s">
-        <x:v>203</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="G2" s="13" t="s">
-        <x:v>204</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H2" s="13" t="s">
-        <x:v>205</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="I2" s="13" t="s">
-        <x:v>206</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="J2" s="13" t="s">
-        <x:v>87</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K2" s="17" t="s">
-        <x:v>200</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="K2" r:id="rId43"/>
+    <x:hyperlink ref="K2" r:id="rId29"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2478,24 +2225,24 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="10" t="s">
-        <x:v>207</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B1" s="10" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1" s="10" t="s">
-        <x:v>208</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3" customFormat="1" ht="29" customHeight="1">
       <x:c r="A2" s="33" t="s">
-        <x:v>209</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B2" s="12" t="s">
-        <x:v>199</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C2" s="12" t="s">
-        <x:v>210</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2527,54 +2274,54 @@
   <x:sheetData>
     <x:row r="1" spans="1:8">
       <x:c r="A1" s="8" t="s">
-        <x:v>211</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B1" s="8" t="s">
-        <x:v>212</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C1" s="8" t="s">
-        <x:v>213</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D1" s="8" t="s">
-        <x:v>214</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E1" s="8" t="s">
-        <x:v>215</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="F1" s="8" t="s">
-        <x:v>216</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G1" s="8" t="s">
-        <x:v>217</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="H1" s="8" t="s">
-        <x:v>218</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" customFormat="1" ht="43.4" customHeight="1">
       <x:c r="A2" s="8" t="s">
-        <x:v>219</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B2" s="8" t="s">
-        <x:v>189</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C2" s="9" t="s">
-        <x:v>220</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E2" s="8" t="s">
-        <x:v>221</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="F2" s="8" t="s">
-        <x:v>222</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G2" s="0" t="n">
         <x:v>587</x:v>
       </x:c>
       <x:c r="H2" s="8" t="s">
-        <x:v>223</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2612,15 +2359,15 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="0" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>3</x:v>
@@ -2629,10 +2376,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -2640,16 +2387,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -2657,16 +2404,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
@@ -2674,16 +2421,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -2691,16 +2438,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
@@ -2708,16 +2455,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
@@ -2725,16 +2472,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
@@ -2742,16 +2489,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
@@ -2759,16 +2506,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
@@ -2776,16 +2523,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
@@ -2793,16 +2540,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
@@ -2810,16 +2557,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
@@ -2827,16 +2574,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
@@ -2844,16 +2591,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
@@ -2861,16 +2608,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
@@ -2878,16 +2625,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
@@ -2895,16 +2642,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
@@ -2912,16 +2659,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
@@ -2929,16 +2676,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
@@ -2946,16 +2693,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
@@ -2963,16 +2710,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
@@ -2980,16 +2727,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
@@ -2997,16 +2744,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
@@ -3014,16 +2761,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
@@ -3031,16 +2778,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
@@ -3048,16 +2795,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
@@ -3065,16 +2812,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3228,16 +2975,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:22" customFormat="1" ht="16" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
         <x:v>243</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
         <x:v>244</x:v>
@@ -3296,7 +3043,7 @@
     </x:row>
     <x:row r="2" spans="1:22" s="1" customFormat="1" ht="58" customHeight="1">
       <x:c r="A2" s="3" t="s">
-        <x:v>73</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="4" t="s">
         <x:v>262</x:v>
@@ -3385,13 +3132,13 @@
   <x:sheetData>
     <x:row r="1" spans="1:6">
       <x:c r="A1" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6">
@@ -3399,10 +3146,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
@@ -3410,10 +3157,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3452,96 +3199,96 @@
   <x:sheetData>
     <x:row r="1" spans="1:15">
       <x:c r="A1" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B1" s="5" t="s">
-        <x:v>59</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C1" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D1" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E1" s="5" t="s">
-        <x:v>62</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F1" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G1" s="5" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H1" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I1" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J1" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K1" s="5" t="s">
-        <x:v>68</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L1" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="M1" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="N1" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="O1" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:15" customFormat="1" ht="116" customHeight="1">
       <x:c r="A2" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C2" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E2" s="5" t="s">
-        <x:v>77</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F2" s="5" t="s">
-        <x:v>78</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G2" s="5" t="s">
-        <x:v>79</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>82</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>83</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L2" s="5" t="s">
-        <x:v>84</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="M2" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="N2" s="3" t="s">
-        <x:v>86</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="O2" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3582,108 +3329,108 @@
   <x:sheetData>
     <x:row r="1" spans="1:17">
       <x:c r="A1" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B1" s="22" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1" s="22" t="s">
-        <x:v>89</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D1" s="22" t="s">
-        <x:v>90</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E1" s="22" t="s">
-        <x:v>91</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F1" s="22" t="s">
-        <x:v>92</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G1" s="22" t="s">
-        <x:v>93</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H1" s="22" t="s">
-        <x:v>94</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I1" s="22" t="s">
-        <x:v>95</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J1" s="22" t="s">
-        <x:v>96</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K1" s="22" t="s">
-        <x:v>97</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L1" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M1" s="28" t="s">
-        <x:v>99</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N1" s="28" t="s">
-        <x:v>100</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O1" s="28" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="P1" s="28" t="s">
-        <x:v>102</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="Q1" s="28" t="s">
-        <x:v>103</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:17">
       <x:c r="A2" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D2" s="26" t="s">
-        <x:v>105</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2" s="26" t="s">
-        <x:v>106</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F2" s="27" t="s">
-        <x:v>107</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G2" s="26" t="s">
-        <x:v>106</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H2" s="26" t="s">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J2" s="26" t="s">
-        <x:v>110</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K2" s="26" t="s">
-        <x:v>111</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="L2" s="18" t="s">
-        <x:v>112</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="O2" s="8" t="s">
-        <x:v>115</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="P2" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Q2" s="8" t="s">
-        <x:v>117</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:17">
@@ -3697,7 +3444,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="L2" r:id="rId21"/>
+    <x:hyperlink ref="L2" r:id="rId20"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3742,132 +3489,132 @@
   <x:sheetData>
     <x:row r="1" spans="1:24">
       <x:c r="A1" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B1" s="22" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1" s="22" t="s">
-        <x:v>89</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D1" s="22" t="s">
-        <x:v>90</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E1" s="22" t="s">
-        <x:v>91</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F1" s="22" t="s">
-        <x:v>92</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G1" s="22" t="s">
-        <x:v>93</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H1" s="22" t="s">
-        <x:v>94</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I1" s="22" t="s">
-        <x:v>95</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J1" s="22" t="s">
-        <x:v>96</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K1" s="22" t="s">
-        <x:v>97</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L1" s="22" t="s">
-        <x:v>118</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="M1" s="22" t="s">
-        <x:v>119</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="N1" s="28" t="s">
-        <x:v>98</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O1" s="28" t="s">
-        <x:v>99</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P1" s="28" t="s">
-        <x:v>100</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="Q1" s="28" t="s">
-        <x:v>101</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R1" s="28" t="s">
-        <x:v>120</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="S1" s="28" t="s">
-        <x:v>121</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="T1" s="28" t="s">
-        <x:v>103</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="U1" s="28" t="s">
-        <x:v>102</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:24" customFormat="1" ht="17.25" customHeight="1">
       <x:c r="A2" s="23" t="s">
-        <x:v>73</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="23" t="s">
-        <x:v>104</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C2" s="23" t="s">
-        <x:v>104</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D2" s="24" t="s">
-        <x:v>105</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E2" s="24" t="s">
-        <x:v>106</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F2" s="25" t="s">
-        <x:v>107</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G2" s="24" t="s">
-        <x:v>106</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H2" s="24" t="s">
-        <x:v>108</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I2" s="23" t="s">
-        <x:v>109</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J2" s="24" t="s">
-        <x:v>110</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K2" s="24" t="s">
-        <x:v>122</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="L2" s="24" t="s">
-        <x:v>111</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M2" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N2" s="18" t="s">
-        <x:v>123</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="O2" s="23" t="s">
-        <x:v>124</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="P2" s="32" t="s">
-        <x:v>125</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q2" s="23" t="s">
-        <x:v>126</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="R2" s="30" t="s">
-        <x:v>127</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="S2" s="31" t="s">
-        <x:v>128</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="T2" s="31" t="s">
-        <x:v>129</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="U2" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:24">
@@ -3907,35 +3654,35 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4" customFormat="1" ht="72.5" customHeight="1">
       <x:c r="A2" s="18" t="s">
-        <x:v>132</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="A2" r:id="rId24"/>
+    <x:hyperlink ref="A2" r:id="rId21"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3959,23 +3706,23 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="18" t="s">
-        <x:v>136</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="A2" r:id="rId25"/>
+    <x:hyperlink ref="A2" r:id="rId22"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4004,96 +3751,96 @@
   <x:sheetData>
     <x:row r="1" spans="1:14" s="1" customFormat="1" ht="73.5" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:14" s="1" customFormat="1" ht="72.65" customHeight="1">
       <x:c r="A2" s="20" t="s">
-        <x:v>148</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B2" s="20" t="s">
-        <x:v>149</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D2" s="9" t="s">
-        <x:v>151</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E2" s="1" t="n">
         <x:v>123</x:v>
       </x:c>
       <x:c r="F2" s="9" t="s">
-        <x:v>152</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G2" s="21" t="s">
-        <x:v>153</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I2" s="1" t="n">
         <x:v>500081</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="M2" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="N2" s="1" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="L2" s="1" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="M2" s="1" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="N2" s="1" t="s">
-        <x:v>157</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="A2" r:id="rId29"/>
-    <x:hyperlink ref="B2" r:id="rId30"/>
+    <x:hyperlink ref="A2" r:id="rId23"/>
+    <x:hyperlink ref="B2" r:id="rId24"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4133,120 +3880,120 @@
   <x:sheetData>
     <x:row r="1" spans="1:21">
       <x:c r="A1" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F1" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G1" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H1" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="I1" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="J1" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="K1" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="L1" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="M1" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="N1" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="O1" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="P1" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="Q1" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="R1" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="S1" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:21">
       <x:c r="A2" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D2" s="18" t="s">
-        <x:v>176</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E2" s="18" t="s">
-        <x:v>177</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F2" s="18" t="s">
-        <x:v>178</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="H2" s="18" t="s">
-        <x:v>180</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="J2" s="8" t="s">
-        <x:v>182</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="L2" s="19" t="s">
-        <x:v>183</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="M2" s="8" t="s">
-        <x:v>184</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="P2" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="Q2" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="R2" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:21">
@@ -4260,10 +4007,10 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink ref="H2" r:id="rId37"/>
-    <x:hyperlink ref="E2" r:id="rId38"/>
-    <x:hyperlink ref="F2" r:id="rId39"/>
-    <x:hyperlink ref="D2" r:id="rId40"/>
+    <x:hyperlink ref="H2" r:id="rId25"/>
+    <x:hyperlink ref="E2" r:id="rId26"/>
+    <x:hyperlink ref="F2" r:id="rId27"/>
+    <x:hyperlink ref="D2" r:id="rId28"/>
   </x:hyperlinks>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
